--- a/Komponenten und Auslegung/Zukaufteile_Bestellliste.xlsx
+++ b/Komponenten und Auslegung/Zukaufteile_Bestellliste.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxec\Documents\Studium\4. Semester\Elektronische Produktentwicklung I\ELEK_Inv_Pen\Komponenten und Auslegung\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1ac616d471f04106/070_UNI/40_SS25/ELEKT/ELEK_Inv_Pen/Komponenten und Auslegung/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7A3EBB-F208-4AF0-8987-65698B934AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{2F7A3EBB-F208-4AF0-8987-65698B934AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E3766BB-30E3-4A4A-AB0A-C237771C7F1B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31725" yWindow="-16200" windowWidth="19410" windowHeight="16305" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>Zukaufteile:</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>https://www.amazon.de/QUPERR-Sicherung-Akku-Adapter-Lithium-Akku-Power-Converter/dp/B0BPRYRGVF/ref=sr_1_6?__mk_de_DE=ÅMÅŽÕÑ&amp;crid=276VZBEJ40QUX&amp;dib=eyJ2IjoiMSJ9.7SKdXH7QLVLBjgwq-4cSCmbfxWZX8zEXSMFm1-XC4fKXJnAK8tr-OUUHGSCVjd96leUb2TzWPY70SoNDNuofOuOwgBoaw3QEOZNwy2e21XDrZdrocEDUCDjjEvyJknbExeVieTLSwac3dbVEVAA3MsZyqtxId76PBSZqhRb2NTPzAfUzjW1d9oUUEX1JwUPF_MGxOsbfKxQzeZp9oAaAs81eWJjCOFA_fS7nYSsUeDY.9tHZQNh8Hzu9MMm-HiRbNy1zVDuVNl88OwXy5J3tccM&amp;dib_tag=se&amp;keywords=makita+akku+schnittstelle&amp;qid=1747144685&amp;sprefix=makita+akku+schnittstell%2Caps%2C146&amp;sr=8-6</t>
+  </si>
+  <si>
+    <t>ESP01</t>
+  </si>
+  <si>
+    <t>ESP8266 ESP-01S WiFi Modul</t>
+  </si>
+  <si>
+    <t>ESP8266 ESP-01S WiFi Modul | Roboter-Bausatz.de</t>
   </si>
 </sst>
 </file>
@@ -415,7 +424,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -444,6 +453,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="2" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="17" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -848,22 +858,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="86.42578125" customWidth="1"/>
-    <col min="3" max="4" width="7.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="255.5703125" customWidth="1"/>
+    <col min="2" max="2" width="86.453125" customWidth="1"/>
+    <col min="3" max="4" width="7.7265625" customWidth="1"/>
+    <col min="5" max="5" width="17.26953125" customWidth="1"/>
+    <col min="6" max="6" width="255.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -883,7 +893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -901,7 +911,7 @@
       </c>
       <c r="F5" s="10"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
@@ -919,7 +929,7 @@
       </c>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
         <v>12</v>
       </c>
@@ -939,7 +949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="16" t="s">
         <v>16</v>
       </c>
@@ -959,7 +969,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
@@ -979,7 +989,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -999,7 +1009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>25</v>
       </c>
@@ -1019,30 +1029,50 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="13">
+        <v>1</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="14">
+        <v>2.75</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B13" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C13" s="24">
         <v>1</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D13" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E13" s="25">
         <v>18</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F13" s="26" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E13" s="27">
-        <f>SUM(E5:E12)</f>
-        <v>238</v>
+    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E14" s="27">
+        <f>SUM(E5:E13)</f>
+        <v>240.75</v>
       </c>
     </row>
   </sheetData>
@@ -1051,7 +1081,8 @@
     <hyperlink ref="F8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="F9" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="F10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="F12" r:id="rId5" display="https://www.amazon.de/QUPERR-Sicherung-Akku-Adapter-Lithium-Akku-Power-Converter/dp/B0BPRYRGVF/ref=sr_1_6?__mk_de_DE=ÅMÅŽÕÑ&amp;crid=276VZBEJ40QUX&amp;dib=eyJ2IjoiMSJ9.7SKdXH7QLVLBjgwq-4cSCmbfxWZX8zEXSMFm1-XC4fKXJnAK8tr-OUUHGSCVjd96leUb2TzWPY70SoNDNuofOuOwgBoaw3QEOZNwy2e21XDrZdrocEDUCDjjEvyJknbExeVieTLSwac3dbVEVAA3MsZyqtxId76PBSZqhRb2NTPzAfUzjW1d9oUUEX1JwUPF_MGxOsbfKxQzeZp9oAaAs81eWJjCOFA_fS7nYSsUeDY.9tHZQNh8Hzu9MMm-HiRbNy1zVDuVNl88OwXy5J3tccM&amp;dib_tag=se&amp;keywords=makita+akku+schnittstelle&amp;qid=1747144685&amp;sprefix=makita+akku+schnittstell%2Caps%2C146&amp;sr=8-6" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F13" r:id="rId5" display="https://www.amazon.de/QUPERR-Sicherung-Akku-Adapter-Lithium-Akku-Power-Converter/dp/B0BPRYRGVF/ref=sr_1_6?__mk_de_DE=ÅMÅŽÕÑ&amp;crid=276VZBEJ40QUX&amp;dib=eyJ2IjoiMSJ9.7SKdXH7QLVLBjgwq-4cSCmbfxWZX8zEXSMFm1-XC4fKXJnAK8tr-OUUHGSCVjd96leUb2TzWPY70SoNDNuofOuOwgBoaw3QEOZNwy2e21XDrZdrocEDUCDjjEvyJknbExeVieTLSwac3dbVEVAA3MsZyqtxId76PBSZqhRb2NTPzAfUzjW1d9oUUEX1JwUPF_MGxOsbfKxQzeZp9oAaAs81eWJjCOFA_fS7nYSsUeDY.9tHZQNh8Hzu9MMm-HiRbNy1zVDuVNl88OwXy5J3tccM&amp;dib_tag=se&amp;keywords=makita+akku+schnittstelle&amp;qid=1747144685&amp;sprefix=makita+akku+schnittstell%2Caps%2C146&amp;sr=8-6" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="F12" r:id="rId6" display="https://www.roboter-bausatz.de/p/ai-thinker-esp8266-esp-01s-wifi-modul" xr:uid="{54A0C8E7-3BB1-4B21-8DCE-13C7DF11CC75}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/Komponenten und Auslegung/Zukaufteile_Bestellliste.xlsx
+++ b/Komponenten und Auslegung/Zukaufteile_Bestellliste.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1ac616d471f04106/070_UNI/40_SS25/ELEKT/ELEK_Inv_Pen/Komponenten und Auslegung/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxec\Documents\Studium\4. Semester\Elektronische Produktentwicklung I\ELEK_Inv_Pen\Komponenten und Auslegung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{2F7A3EBB-F208-4AF0-8987-65698B934AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E3766BB-30E3-4A4A-AB0A-C237771C7F1B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C801E07-F1E3-418A-91BC-DDBE4CA3EF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31725" yWindow="-16200" windowWidth="19410" windowHeight="16305" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -859,21 +859,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="86.453125" customWidth="1"/>
-    <col min="3" max="4" width="7.7265625" customWidth="1"/>
-    <col min="5" max="5" width="17.26953125" customWidth="1"/>
-    <col min="6" max="6" width="255.54296875" customWidth="1"/>
+    <col min="2" max="2" width="86.42578125" customWidth="1"/>
+    <col min="3" max="4" width="7.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="255.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -893,7 +893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -911,7 +911,7 @@
       </c>
       <c r="F5" s="10"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
@@ -929,7 +929,7 @@
       </c>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>12</v>
       </c>
@@ -949,7 +949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>16</v>
       </c>
@@ -969,7 +969,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
@@ -989,7 +989,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>25</v>
       </c>
@@ -1029,7 +1029,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>28</v>
       </c>
@@ -1069,7 +1069,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E14" s="27">
         <f>SUM(E5:E13)</f>
         <v>240.75</v>
